--- a/output/roomself_excel/12278.xlsx
+++ b/output/roomself_excel/12278.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>304810</v>
+        <v>59908</v>
       </c>
       <c r="D2" t="n">
-        <v>6412</v>
+        <v>2036</v>
       </c>
       <c r="E2" t="n">
-        <v>857</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57996</v>
+        <v>168300</v>
       </c>
       <c r="D3" t="n">
-        <v>2012</v>
+        <v>3296</v>
       </c>
       <c r="E3" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80676</v>
+        <v>29610</v>
       </c>
       <c r="D4" t="n">
-        <v>2292</v>
+        <v>1404</v>
       </c>
       <c r="E4" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,14 +532,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29610</v>
+        <v>76602</v>
       </c>
       <c r="D5" t="n">
-        <v>1404</v>
+        <v>2532</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -564,10 +564,10 @@
         <v>1024</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17685</v>
+        <v>57996</v>
       </c>
       <c r="D7" t="n">
-        <v>1064</v>
+        <v>2012</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2346</v>
+        <v>80676</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>2292</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,15 +624,59 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>17685</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1064</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2346</v>
+      </c>
+      <c r="D10" t="n">
+        <v>388</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>360</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>168</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/roomself_excel/12278.xlsx
+++ b/output/roomself_excel/12278.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
         </is>
       </c>
     </row>
@@ -475,12 +480,9 @@
       <c r="D2" t="n">
         <v>2036</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +499,9 @@
       <c r="D3" t="n">
         <v>3296</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +518,9 @@
       <c r="D4" t="n">
         <v>1404</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +537,9 @@
       <c r="D5" t="n">
         <v>2532</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +556,16 @@
       <c r="D6" t="n">
         <v>1024</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +583,9 @@
       <c r="D7" t="n">
         <v>2012</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +602,9 @@
       <c r="D8" t="n">
         <v>2292</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +621,9 @@
       <c r="D9" t="n">
         <v>1064</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +640,9 @@
       <c r="D10" t="n">
         <v>388</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +659,9 @@
       <c r="D11" t="n">
         <v>168</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
